--- a/E2E_Test_Report_TMS_2026-06-11T13-25-23.xlsx
+++ b/E2E_Test_Report_TMS_2026-06-11T13-25-23.xlsx
@@ -497,12 +497,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-11 13:19:25</t>
+          <t>2026-06-13 12:55:11</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-11 13:25:23</t>
+          <t>2026-06-13 12:55:11</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -587,7 +586,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -608,7 +606,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -629,7 +626,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -650,7 +646,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -671,7 +666,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -692,7 +686,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -713,7 +706,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -734,7 +726,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -755,7 +746,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -776,7 +766,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -797,7 +786,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -818,7 +806,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -839,7 +826,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -860,7 +846,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -881,7 +866,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -902,7 +886,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -923,7 +906,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -944,7 +926,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -965,7 +946,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -986,7 +966,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1007,7 +986,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1028,7 +1006,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1049,7 +1026,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1070,7 +1046,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1091,7 +1066,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1112,7 +1086,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1133,7 +1106,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1154,7 +1126,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1175,7 +1146,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1196,7 +1166,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1217,7 +1186,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1238,7 +1206,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1259,7 +1226,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1280,7 +1246,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1301,7 +1266,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1322,7 +1286,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1343,7 +1306,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1364,7 +1326,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1385,7 +1346,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1406,7 +1366,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1427,7 +1386,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1448,7 +1406,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1469,7 +1426,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1490,7 +1446,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1511,7 +1466,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1532,7 +1486,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1553,7 +1506,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1574,7 +1526,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1595,7 +1546,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1616,7 +1566,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1637,7 +1586,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1658,7 +1606,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1679,7 +1626,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1700,7 +1646,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1721,7 +1666,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1742,7 +1686,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1763,7 +1706,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1784,7 +1726,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1805,7 +1746,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1826,7 +1766,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1847,7 +1786,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1868,7 +1806,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1889,7 +1826,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1910,7 +1846,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1931,7 +1866,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1952,7 +1886,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1973,7 +1906,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1994,7 +1926,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2015,7 +1946,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2036,7 +1966,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2057,7 +1986,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2078,7 +2006,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2099,7 +2026,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2120,7 +2046,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2141,7 +2066,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2162,7 +2086,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2183,7 +2106,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2204,7 +2126,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2225,7 +2146,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2246,7 +2166,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2267,7 +2186,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2288,7 +2206,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2309,7 +2226,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2330,7 +2246,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -2351,7 +2266,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2372,7 +2286,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -2393,7 +2306,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2414,7 +2326,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2435,7 +2346,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2456,7 +2366,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -2477,7 +2386,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2498,7 +2406,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -2519,7 +2426,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -2540,7 +2446,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -2561,7 +2466,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -2582,7 +2486,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -2603,7 +2506,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -2624,7 +2526,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -2645,7 +2546,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2748,7 +2648,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2769,7 +2668,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2790,7 +2688,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2811,7 +2708,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2832,7 +2728,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2853,7 +2748,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2874,7 +2768,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2895,7 +2788,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2916,7 +2808,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2937,7 +2828,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2958,7 +2848,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2979,7 +2868,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3000,7 +2888,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -3021,7 +2908,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -3042,7 +2928,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3063,7 +2948,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3084,7 +2968,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3105,7 +2988,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3126,7 +3008,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3147,7 +3028,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3168,7 +3048,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3189,7 +3068,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3210,7 +3088,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3231,7 +3108,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3252,7 +3128,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3273,7 +3148,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3294,7 +3168,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3315,7 +3188,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3336,7 +3208,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3357,7 +3228,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3378,7 +3248,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3399,7 +3268,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3420,7 +3288,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3441,7 +3308,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3462,7 +3328,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3483,7 +3348,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3504,7 +3368,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3525,7 +3388,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3546,7 +3408,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3567,7 +3428,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3588,7 +3448,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3609,7 +3468,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3630,7 +3488,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3651,7 +3508,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3672,7 +3528,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3693,7 +3548,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3714,7 +3568,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3735,7 +3588,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3756,7 +3608,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3777,7 +3628,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3798,7 +3648,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3819,7 +3668,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3840,7 +3688,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3861,7 +3708,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3882,7 +3728,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3903,7 +3748,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3924,7 +3768,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3945,7 +3788,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3966,7 +3808,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3987,7 +3828,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4008,7 +3848,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4029,7 +3868,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4050,7 +3888,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4071,7 +3908,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4092,7 +3928,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4113,7 +3948,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4134,7 +3968,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4155,7 +3988,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4176,7 +4008,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4197,7 +4028,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4218,7 +4048,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4239,7 +4068,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4260,7 +4088,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4281,7 +4108,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4302,7 +4128,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4323,7 +4148,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4344,7 +4168,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4365,7 +4188,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4386,7 +4208,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4407,7 +4228,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4428,7 +4248,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4449,7 +4268,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4470,7 +4288,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4491,7 +4308,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -4512,7 +4328,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4533,7 +4348,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4554,7 +4368,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -4575,7 +4388,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -4596,7 +4408,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4617,7 +4428,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4638,7 +4448,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -4659,7 +4468,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4680,7 +4488,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4701,7 +4508,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4722,7 +4528,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4743,7 +4548,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4764,7 +4568,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4785,7 +4588,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4806,7 +4608,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4827,7 +4628,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4889,7 +4689,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -4910,7 +4709,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4931,7 +4729,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -4952,7 +4749,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4973,7 +4769,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4994,7 +4789,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -5015,7 +4809,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5036,7 +4829,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -5057,7 +4849,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -5078,7 +4869,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -5099,7 +4889,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -5120,7 +4909,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -5141,7 +4929,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -5162,7 +4949,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -5183,7 +4969,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -5204,7 +4989,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -5225,7 +5009,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -5246,7 +5029,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -5267,7 +5049,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -5288,7 +5069,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -5309,7 +5089,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -5330,7 +5109,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5351,7 +5129,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -5372,7 +5149,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -5393,7 +5169,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -5414,7 +5189,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -5435,7 +5209,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -5456,7 +5229,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -5477,7 +5249,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -5498,7 +5269,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -5519,7 +5289,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5540,7 +5309,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5561,7 +5329,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5582,7 +5349,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5603,7 +5369,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5624,7 +5389,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5645,7 +5409,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5666,7 +5429,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5687,7 +5449,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5708,7 +5469,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5729,7 +5489,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5750,7 +5509,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5771,7 +5529,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5792,7 +5549,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5813,7 +5569,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5834,7 +5589,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5855,7 +5609,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5876,7 +5629,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5897,7 +5649,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5918,7 +5669,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5939,7 +5689,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5960,7 +5709,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5981,7 +5729,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6002,7 +5749,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6023,7 +5769,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6044,7 +5789,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6065,7 +5809,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6086,7 +5829,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6107,7 +5849,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6128,7 +5869,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6149,7 +5889,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6170,7 +5909,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6191,7 +5929,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6212,7 +5949,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6233,7 +5969,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -6254,7 +5989,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -6275,7 +6009,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -6296,7 +6029,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -6317,7 +6049,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -6338,7 +6069,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -6359,7 +6089,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -6380,7 +6109,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -6401,7 +6129,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -6422,7 +6149,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -6443,7 +6169,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -6464,7 +6189,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -6485,7 +6209,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -6506,7 +6229,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -6527,7 +6249,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -6548,7 +6269,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6569,7 +6289,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6590,7 +6309,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -6611,7 +6329,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6632,7 +6349,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6653,7 +6369,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -6674,7 +6389,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -6695,7 +6409,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6716,7 +6429,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -6737,7 +6449,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6758,7 +6469,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -6779,7 +6489,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -6800,7 +6509,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6821,7 +6529,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6842,7 +6549,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6863,7 +6569,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6884,7 +6589,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6905,7 +6609,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6926,7 +6629,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6947,7 +6649,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6968,7 +6669,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
